--- a/internal/migration/Defab Thrippunithura/DYBL MTRL.xlsx
+++ b/internal/migration/Defab Thrippunithura/DYBL MTRL.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QMark\defab_erp_backend\internal\migration\Defab Thrippunithura\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/44ad478e1d2bb188/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D68372-CA89-4CA2-BD15-0F9D2A5D711A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_1B46CFA5A2602A58FFEB19DB636D038902E77D53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B115A397-2A57-4734-B176-1D8C2C401F85}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="10">
   <si>
     <t>SL .NO</t>
   </si>
@@ -45,6 +45,18 @@
   </si>
   <si>
     <t>DYBL MTRL</t>
+  </si>
+  <si>
+    <t>NEW MRP EXCLUDING GST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXABLE </t>
+  </si>
+  <si>
+    <t>TAX</t>
+  </si>
+  <si>
+    <t>MRP</t>
   </si>
 </sst>
 </file>
@@ -86,9 +98,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -149,7 +162,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -184,7 +197,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -369,13 +382,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E93"/>
+  <dimension ref="A2:J93"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="6" max="6" width="27.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -391,8 +405,11 @@
       <c r="E2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -408,8 +425,24 @@
       <c r="E3">
         <v>375</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <f>ROUND(IF(E3&gt;2500, E3/1.18, E3/1.05),2)</f>
+        <v>357.14</v>
+      </c>
+      <c r="H3">
+        <f>ROUND(IF(E3&gt;2500, E3/1.18, E3/1.05),2)</f>
+        <v>357.14</v>
+      </c>
+      <c r="I3">
+        <f>E3-F3</f>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J3">
+        <f>SUM(H3:I3)</f>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>5217</v>
       </c>
@@ -422,8 +455,24 @@
       <c r="E4">
         <v>215</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <f t="shared" ref="F4:F67" si="0">ROUND(IF(E4&gt;2500, E4/1.18, E4/1.05),2)</f>
+        <v>204.76</v>
+      </c>
+      <c r="H4">
+        <f t="shared" ref="H4:H67" si="1">ROUND(IF(E4&gt;2500, E4/1.18, E4/1.05),2)</f>
+        <v>204.76</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I4:I67" si="2">E4-F4</f>
+        <v>10.240000000000009</v>
+      </c>
+      <c r="J4">
+        <f t="shared" ref="J4:J67" si="3">SUM(H4:I4)</f>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>5217</v>
       </c>
@@ -436,8 +485,24 @@
       <c r="E5">
         <v>215</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>204.76</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>204.76</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="2"/>
+        <v>10.240000000000009</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="3"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>2804</v>
       </c>
@@ -450,8 +515,24 @@
       <c r="E6">
         <v>265</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>252.38</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>252.38</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="2"/>
+        <v>12.620000000000005</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="3"/>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>2810</v>
       </c>
@@ -464,8 +545,24 @@
       <c r="E7">
         <v>350</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>333.33</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>333.33</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="2"/>
+        <v>16.670000000000016</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="3"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>5218</v>
       </c>
@@ -478,8 +575,24 @@
       <c r="E8">
         <v>375</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>5219</v>
       </c>
@@ -492,8 +605,24 @@
       <c r="E9">
         <v>375</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>5217</v>
       </c>
@@ -506,8 +635,24 @@
       <c r="E10">
         <v>215</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>204.76</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>204.76</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="2"/>
+        <v>10.240000000000009</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="3"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>2801</v>
       </c>
@@ -520,8 +665,24 @@
       <c r="E11">
         <v>595</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>566.66999999999996</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>566.66999999999996</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="2"/>
+        <v>28.330000000000041</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="3"/>
+        <v>595</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>2803</v>
       </c>
@@ -534,8 +695,24 @@
       <c r="E12">
         <v>255</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>242.86</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>242.86</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="2"/>
+        <v>12.139999999999986</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>5218</v>
       </c>
@@ -548,8 +725,24 @@
       <c r="E13">
         <v>375</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>5217</v>
       </c>
@@ -562,8 +755,24 @@
       <c r="E14">
         <v>215</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>204.76</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>204.76</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="2"/>
+        <v>10.240000000000009</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="3"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>5038</v>
       </c>
@@ -576,8 +785,24 @@
       <c r="E15">
         <v>350</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>333.33</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>333.33</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="2"/>
+        <v>16.670000000000016</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="3"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>2803</v>
       </c>
@@ -590,8 +815,24 @@
       <c r="E16">
         <v>255</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>242.86</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>242.86</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="2"/>
+        <v>12.139999999999986</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>5063</v>
       </c>
@@ -604,8 +845,24 @@
       <c r="E17">
         <v>255</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>242.86</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>242.86</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="2"/>
+        <v>12.139999999999986</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>2807</v>
       </c>
@@ -618,8 +875,24 @@
       <c r="E18">
         <v>290</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>276.19</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>276.19</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="2"/>
+        <v>13.810000000000002</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="3"/>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>5063</v>
       </c>
@@ -632,8 +905,24 @@
       <c r="E19">
         <v>255</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>242.86</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>242.86</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="2"/>
+        <v>12.139999999999986</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>2803</v>
       </c>
@@ -646,8 +935,24 @@
       <c r="E20">
         <v>255</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>242.86</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>242.86</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="2"/>
+        <v>12.139999999999986</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>5218</v>
       </c>
@@ -660,8 +965,24 @@
       <c r="E21">
         <v>375</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>5219</v>
       </c>
@@ -674,8 +995,24 @@
       <c r="E22">
         <v>375</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>5219</v>
       </c>
@@ -688,8 +1025,24 @@
       <c r="E23">
         <v>375</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>2803</v>
       </c>
@@ -702,8 +1055,24 @@
       <c r="E24">
         <v>255</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>242.86</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>242.86</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="2"/>
+        <v>12.139999999999986</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>5219</v>
       </c>
@@ -716,8 +1085,24 @@
       <c r="E25">
         <v>375</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>5218</v>
       </c>
@@ -730,8 +1115,24 @@
       <c r="E26">
         <v>375</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>2799</v>
       </c>
@@ -744,8 +1145,24 @@
       <c r="E27">
         <v>470</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>447.62</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>447.62</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="2"/>
+        <v>22.379999999999995</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="3"/>
+        <v>470</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>5217</v>
       </c>
@@ -758,8 +1175,24 @@
       <c r="E28">
         <v>215</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>204.76</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="1"/>
+        <v>204.76</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="2"/>
+        <v>10.240000000000009</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="3"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>5218</v>
       </c>
@@ -772,8 +1205,24 @@
       <c r="E29">
         <v>375</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>5219</v>
       </c>
@@ -786,8 +1235,24 @@
       <c r="E30">
         <v>375</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>2799</v>
       </c>
@@ -800,8 +1265,24 @@
       <c r="E31">
         <v>470</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>447.62</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="1"/>
+        <v>447.62</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="2"/>
+        <v>22.379999999999995</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="3"/>
+        <v>470</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>5035</v>
       </c>
@@ -814,8 +1295,24 @@
       <c r="E32">
         <v>350</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>333.33</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>333.33</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="2"/>
+        <v>16.670000000000016</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="3"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>2805</v>
       </c>
@@ -828,8 +1325,24 @@
       <c r="E33">
         <v>135</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>128.57</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="1"/>
+        <v>128.57</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="2"/>
+        <v>6.4300000000000068</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="3"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>5063</v>
       </c>
@@ -842,8 +1355,24 @@
       <c r="E34">
         <v>255</v>
       </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>242.86</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>242.86</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="2"/>
+        <v>12.139999999999986</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>2807</v>
       </c>
@@ -856,8 +1385,24 @@
       <c r="E35">
         <v>290</v>
       </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>276.19</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="1"/>
+        <v>276.19</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="2"/>
+        <v>13.810000000000002</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="3"/>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>2804</v>
       </c>
@@ -870,8 +1415,24 @@
       <c r="E36">
         <v>265</v>
       </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>252.38</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="1"/>
+        <v>252.38</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="2"/>
+        <v>12.620000000000005</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="3"/>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>5219</v>
       </c>
@@ -884,8 +1445,24 @@
       <c r="E37">
         <v>375</v>
       </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>3343</v>
       </c>
@@ -898,8 +1475,24 @@
       <c r="E38">
         <v>490</v>
       </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>466.67</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>466.67</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="2"/>
+        <v>23.329999999999984</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="3"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>4219</v>
       </c>
@@ -912,8 +1505,24 @@
       <c r="E39">
         <v>375</v>
       </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>5063</v>
       </c>
@@ -926,8 +1535,24 @@
       <c r="E40">
         <v>255</v>
       </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>242.86</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>242.86</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="2"/>
+        <v>12.139999999999986</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>5063</v>
       </c>
@@ -940,8 +1565,24 @@
       <c r="E41">
         <v>255</v>
       </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>242.86</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="1"/>
+        <v>242.86</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="2"/>
+        <v>12.139999999999986</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>5063</v>
       </c>
@@ -954,8 +1595,24 @@
       <c r="E42">
         <v>255</v>
       </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F42">
+        <f t="shared" si="0"/>
+        <v>242.86</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>242.86</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="2"/>
+        <v>12.139999999999986</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>2803</v>
       </c>
@@ -968,8 +1625,24 @@
       <c r="E43">
         <v>255</v>
       </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F43">
+        <f t="shared" si="0"/>
+        <v>242.86</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="1"/>
+        <v>242.86</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="2"/>
+        <v>12.139999999999986</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>2810</v>
       </c>
@@ -982,8 +1655,24 @@
       <c r="E44">
         <v>350</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F44">
+        <f t="shared" si="0"/>
+        <v>333.33</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="1"/>
+        <v>333.33</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="2"/>
+        <v>16.670000000000016</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="3"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>1535</v>
       </c>
@@ -996,8 +1685,24 @@
       <c r="E45">
         <v>185</v>
       </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F45">
+        <f t="shared" si="0"/>
+        <v>176.19</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="1"/>
+        <v>176.19</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="2"/>
+        <v>8.8100000000000023</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>1535</v>
       </c>
@@ -1010,8 +1715,24 @@
       <c r="E46">
         <v>185</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F46">
+        <f t="shared" si="0"/>
+        <v>176.19</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="1"/>
+        <v>176.19</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="2"/>
+        <v>8.8100000000000023</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>1535</v>
       </c>
@@ -1024,8 +1745,24 @@
       <c r="E47">
         <v>185</v>
       </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F47">
+        <f t="shared" si="0"/>
+        <v>176.19</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="1"/>
+        <v>176.19</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="2"/>
+        <v>8.8100000000000023</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>1535</v>
       </c>
@@ -1038,8 +1775,24 @@
       <c r="E48">
         <v>185</v>
       </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F48">
+        <f t="shared" si="0"/>
+        <v>176.19</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="1"/>
+        <v>176.19</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="2"/>
+        <v>8.8100000000000023</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>2800</v>
       </c>
@@ -1052,8 +1805,24 @@
       <c r="E49">
         <v>565</v>
       </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F49">
+        <f t="shared" si="0"/>
+        <v>538.1</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="1"/>
+        <v>538.1</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="2"/>
+        <v>26.899999999999977</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="3"/>
+        <v>565</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>1538</v>
       </c>
@@ -1066,8 +1835,24 @@
       <c r="E50">
         <v>185</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F50">
+        <f t="shared" si="0"/>
+        <v>176.19</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="1"/>
+        <v>176.19</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="2"/>
+        <v>8.8100000000000023</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>10</v>
       </c>
@@ -1080,8 +1865,24 @@
       <c r="E51">
         <v>455</v>
       </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F51">
+        <f t="shared" si="0"/>
+        <v>433.33</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="1"/>
+        <v>433.33</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="2"/>
+        <v>21.670000000000016</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="3"/>
+        <v>455</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>5038</v>
       </c>
@@ -1094,8 +1895,24 @@
       <c r="E52">
         <v>350</v>
       </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F52">
+        <f t="shared" si="0"/>
+        <v>333.33</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="1"/>
+        <v>333.33</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="2"/>
+        <v>16.670000000000016</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="3"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>5588</v>
       </c>
@@ -1108,8 +1925,24 @@
       <c r="E53">
         <v>160</v>
       </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F53">
+        <f t="shared" si="0"/>
+        <v>152.38</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="1"/>
+        <v>152.38</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="2"/>
+        <v>7.6200000000000045</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="3"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>3254</v>
       </c>
@@ -1122,8 +1955,24 @@
       <c r="E54">
         <v>410</v>
       </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F54">
+        <f t="shared" si="0"/>
+        <v>390.48</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="1"/>
+        <v>390.48</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="2"/>
+        <v>19.519999999999982</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="3"/>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>1449</v>
       </c>
@@ -1136,8 +1985,24 @@
       <c r="E55">
         <v>165</v>
       </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F55">
+        <f t="shared" si="0"/>
+        <v>157.13999999999999</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="1"/>
+        <v>157.13999999999999</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="2"/>
+        <v>7.8600000000000136</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="3"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>5218</v>
       </c>
@@ -1150,8 +2015,24 @@
       <c r="E56">
         <v>375</v>
       </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F56">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>3122</v>
       </c>
@@ -1164,8 +2045,24 @@
       <c r="E57">
         <v>635</v>
       </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F57">
+        <f t="shared" si="0"/>
+        <v>604.76</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="1"/>
+        <v>604.76</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="2"/>
+        <v>30.240000000000009</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="3"/>
+        <v>635</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>3283</v>
       </c>
@@ -1178,8 +2075,24 @@
       <c r="E58">
         <v>295</v>
       </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F58">
+        <f t="shared" si="0"/>
+        <v>280.95</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="1"/>
+        <v>280.95</v>
+      </c>
+      <c r="I58">
+        <f t="shared" si="2"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="3"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>1333</v>
       </c>
@@ -1192,8 +2105,24 @@
       <c r="E59">
         <v>165</v>
       </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F59">
+        <f t="shared" si="0"/>
+        <v>157.13999999999999</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="1"/>
+        <v>157.13999999999999</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="2"/>
+        <v>7.8600000000000136</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="3"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>3234</v>
       </c>
@@ -1206,8 +2135,24 @@
       <c r="E60">
         <v>275</v>
       </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F60">
+        <f t="shared" si="0"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="1"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="2"/>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="3"/>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>5219</v>
       </c>
@@ -1220,8 +2165,24 @@
       <c r="E61">
         <v>375</v>
       </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F61">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I61">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>5218</v>
       </c>
@@ -1234,8 +2195,24 @@
       <c r="E62">
         <v>375</v>
       </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F62">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I62">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>872</v>
       </c>
@@ -1248,8 +2225,24 @@
       <c r="E63">
         <v>115</v>
       </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F63">
+        <f t="shared" si="0"/>
+        <v>109.52</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="1"/>
+        <v>109.52</v>
+      </c>
+      <c r="I63">
+        <f t="shared" si="2"/>
+        <v>5.480000000000004</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="3"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>2805</v>
       </c>
@@ -1262,8 +2255,24 @@
       <c r="E64">
         <v>135</v>
       </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F64">
+        <f t="shared" si="0"/>
+        <v>128.57</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="1"/>
+        <v>128.57</v>
+      </c>
+      <c r="I64">
+        <f t="shared" si="2"/>
+        <v>6.4300000000000068</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="3"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>2805</v>
       </c>
@@ -1276,8 +2285,24 @@
       <c r="E65">
         <v>135</v>
       </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F65">
+        <f t="shared" si="0"/>
+        <v>128.57</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="1"/>
+        <v>128.57</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="2"/>
+        <v>6.4300000000000068</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="3"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>2831</v>
       </c>
@@ -1290,8 +2315,24 @@
       <c r="E66">
         <v>495</v>
       </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F66">
+        <f t="shared" si="0"/>
+        <v>471.43</v>
+      </c>
+      <c r="H66">
+        <f t="shared" si="1"/>
+        <v>471.43</v>
+      </c>
+      <c r="I66">
+        <f t="shared" si="2"/>
+        <v>23.569999999999993</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="3"/>
+        <v>495</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>3143</v>
       </c>
@@ -1304,8 +2345,24 @@
       <c r="E67">
         <v>510</v>
       </c>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F67">
+        <f t="shared" si="0"/>
+        <v>485.71</v>
+      </c>
+      <c r="H67">
+        <f t="shared" si="1"/>
+        <v>485.71</v>
+      </c>
+      <c r="I67">
+        <f t="shared" si="2"/>
+        <v>24.29000000000002</v>
+      </c>
+      <c r="J67">
+        <f t="shared" si="3"/>
+        <v>510</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>5037</v>
       </c>
@@ -1318,8 +2375,24 @@
       <c r="E68">
         <v>135</v>
       </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F68">
+        <f t="shared" ref="F68:F93" si="4">ROUND(IF(E68&gt;2500, E68/1.18, E68/1.05),2)</f>
+        <v>128.57</v>
+      </c>
+      <c r="H68">
+        <f t="shared" ref="H68:H93" si="5">ROUND(IF(E68&gt;2500, E68/1.18, E68/1.05),2)</f>
+        <v>128.57</v>
+      </c>
+      <c r="I68">
+        <f t="shared" ref="I68:I93" si="6">E68-F68</f>
+        <v>6.4300000000000068</v>
+      </c>
+      <c r="J68">
+        <f t="shared" ref="J68:J93" si="7">SUM(H68:I68)</f>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>274</v>
       </c>
@@ -1332,8 +2405,24 @@
       <c r="E69">
         <v>525</v>
       </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F69">
+        <f t="shared" si="4"/>
+        <v>500</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="5"/>
+        <v>500</v>
+      </c>
+      <c r="I69">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="7"/>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>3252</v>
       </c>
@@ -1346,8 +2435,24 @@
       <c r="E70">
         <v>360</v>
       </c>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F70">
+        <f t="shared" si="4"/>
+        <v>342.86</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="5"/>
+        <v>342.86</v>
+      </c>
+      <c r="I70">
+        <f t="shared" si="6"/>
+        <v>17.139999999999986</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="7"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>3213</v>
       </c>
@@ -1360,8 +2465,24 @@
       <c r="E71">
         <v>135</v>
       </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F71">
+        <f t="shared" si="4"/>
+        <v>128.57</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="5"/>
+        <v>128.57</v>
+      </c>
+      <c r="I71">
+        <f t="shared" si="6"/>
+        <v>6.4300000000000068</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="7"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>2932</v>
       </c>
@@ -1374,8 +2495,24 @@
       <c r="E72">
         <v>620</v>
       </c>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F72">
+        <f t="shared" si="4"/>
+        <v>590.48</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="5"/>
+        <v>590.48</v>
+      </c>
+      <c r="I72">
+        <f t="shared" si="6"/>
+        <v>29.519999999999982</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="7"/>
+        <v>620</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>2811</v>
       </c>
@@ -1388,8 +2525,24 @@
       <c r="E73">
         <v>340</v>
       </c>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F73">
+        <f t="shared" si="4"/>
+        <v>323.81</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="5"/>
+        <v>323.81</v>
+      </c>
+      <c r="I73">
+        <f t="shared" si="6"/>
+        <v>16.189999999999998</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="7"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>3238</v>
       </c>
@@ -1402,8 +2555,24 @@
       <c r="E74">
         <v>445</v>
       </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F74">
+        <f t="shared" si="4"/>
+        <v>423.81</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="5"/>
+        <v>423.81</v>
+      </c>
+      <c r="I74">
+        <f t="shared" si="6"/>
+        <v>21.189999999999998</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="7"/>
+        <v>445</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>3341</v>
       </c>
@@ -1416,8 +2585,24 @@
       <c r="E75">
         <v>655</v>
       </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F75">
+        <f t="shared" si="4"/>
+        <v>623.80999999999995</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="5"/>
+        <v>623.80999999999995</v>
+      </c>
+      <c r="I75">
+        <f t="shared" si="6"/>
+        <v>31.190000000000055</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="7"/>
+        <v>655</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>2878</v>
       </c>
@@ -1430,8 +2615,24 @@
       <c r="E76">
         <v>635</v>
       </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F76">
+        <f t="shared" si="4"/>
+        <v>604.76</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="5"/>
+        <v>604.76</v>
+      </c>
+      <c r="I76">
+        <f t="shared" si="6"/>
+        <v>30.240000000000009</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="7"/>
+        <v>635</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>2807</v>
       </c>
@@ -1444,8 +2645,24 @@
       <c r="E77">
         <v>290</v>
       </c>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F77">
+        <f t="shared" si="4"/>
+        <v>276.19</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="5"/>
+        <v>276.19</v>
+      </c>
+      <c r="I77">
+        <f t="shared" si="6"/>
+        <v>13.810000000000002</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="7"/>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>2934</v>
       </c>
@@ -1458,8 +2675,24 @@
       <c r="E78">
         <v>1050</v>
       </c>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F78">
+        <f t="shared" si="4"/>
+        <v>1000</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="5"/>
+        <v>1000</v>
+      </c>
+      <c r="I78">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="7"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>2928</v>
       </c>
@@ -1472,8 +2705,24 @@
       <c r="E79">
         <v>625</v>
       </c>
-    </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F79">
+        <f t="shared" si="4"/>
+        <v>595.24</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="5"/>
+        <v>595.24</v>
+      </c>
+      <c r="I79">
+        <f t="shared" si="6"/>
+        <v>29.759999999999991</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="7"/>
+        <v>625</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>3245</v>
       </c>
@@ -1486,8 +2735,24 @@
       <c r="E80">
         <v>750</v>
       </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F80">
+        <f t="shared" si="4"/>
+        <v>714.29</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="5"/>
+        <v>714.29</v>
+      </c>
+      <c r="I80">
+        <f t="shared" si="6"/>
+        <v>35.710000000000036</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="7"/>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>3344</v>
       </c>
@@ -1500,8 +2765,24 @@
       <c r="E81">
         <v>950</v>
       </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F81">
+        <f t="shared" si="4"/>
+        <v>904.76</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="5"/>
+        <v>904.76</v>
+      </c>
+      <c r="I81">
+        <f t="shared" si="6"/>
+        <v>45.240000000000009</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="7"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>2773</v>
       </c>
@@ -1514,8 +2795,24 @@
       <c r="E82">
         <v>595</v>
       </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F82">
+        <f t="shared" si="4"/>
+        <v>566.66999999999996</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="5"/>
+        <v>566.66999999999996</v>
+      </c>
+      <c r="I82">
+        <f t="shared" si="6"/>
+        <v>28.330000000000041</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="7"/>
+        <v>595</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>2808</v>
       </c>
@@ -1528,8 +2825,24 @@
       <c r="E83">
         <v>370</v>
       </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F83">
+        <f t="shared" si="4"/>
+        <v>352.38</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="5"/>
+        <v>352.38</v>
+      </c>
+      <c r="I83">
+        <f t="shared" si="6"/>
+        <v>17.620000000000005</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="7"/>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>2780</v>
       </c>
@@ -1542,8 +2855,24 @@
       <c r="E84">
         <v>900</v>
       </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F84">
+        <f t="shared" si="4"/>
+        <v>857.14</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="5"/>
+        <v>857.14</v>
+      </c>
+      <c r="I84">
+        <f t="shared" si="6"/>
+        <v>42.860000000000014</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="7"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>1528</v>
       </c>
@@ -1556,8 +2885,24 @@
       <c r="E85">
         <v>395</v>
       </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F85">
+        <f t="shared" si="4"/>
+        <v>376.19</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="5"/>
+        <v>376.19</v>
+      </c>
+      <c r="I85">
+        <f t="shared" si="6"/>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="7"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>4337</v>
       </c>
@@ -1570,8 +2915,24 @@
       <c r="E86">
         <v>495</v>
       </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F86">
+        <f t="shared" si="4"/>
+        <v>471.43</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="5"/>
+        <v>471.43</v>
+      </c>
+      <c r="I86">
+        <f t="shared" si="6"/>
+        <v>23.569999999999993</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="7"/>
+        <v>495</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>2930</v>
       </c>
@@ -1584,8 +2945,24 @@
       <c r="E87">
         <v>510</v>
       </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F87">
+        <f t="shared" si="4"/>
+        <v>485.71</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="5"/>
+        <v>485.71</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="6"/>
+        <v>24.29000000000002</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="7"/>
+        <v>510</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>173</v>
       </c>
@@ -1598,8 +2975,24 @@
       <c r="E88">
         <v>175</v>
       </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F88">
+        <f t="shared" si="4"/>
+        <v>166.67</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="5"/>
+        <v>166.67</v>
+      </c>
+      <c r="I88">
+        <f t="shared" si="6"/>
+        <v>8.3300000000000125</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="7"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>2778</v>
       </c>
@@ -1612,8 +3005,24 @@
       <c r="E89">
         <v>430</v>
       </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F89">
+        <f t="shared" si="4"/>
+        <v>409.52</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="5"/>
+        <v>409.52</v>
+      </c>
+      <c r="I89">
+        <f t="shared" si="6"/>
+        <v>20.480000000000018</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="7"/>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>3388</v>
       </c>
@@ -1626,8 +3035,24 @@
       <c r="E90">
         <v>410</v>
       </c>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F90">
+        <f t="shared" si="4"/>
+        <v>390.48</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="5"/>
+        <v>390.48</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="6"/>
+        <v>19.519999999999982</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="7"/>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>3250</v>
       </c>
@@ -1640,8 +3065,24 @@
       <c r="E91">
         <v>995</v>
       </c>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F91">
+        <f t="shared" si="4"/>
+        <v>947.62</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="5"/>
+        <v>947.62</v>
+      </c>
+      <c r="I91">
+        <f t="shared" si="6"/>
+        <v>47.379999999999995</v>
+      </c>
+      <c r="J91">
+        <f t="shared" si="7"/>
+        <v>995</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>276</v>
       </c>
@@ -1654,8 +3095,24 @@
       <c r="E92">
         <v>475</v>
       </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F92">
+        <f t="shared" si="4"/>
+        <v>452.38</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="5"/>
+        <v>452.38</v>
+      </c>
+      <c r="I92">
+        <f t="shared" si="6"/>
+        <v>22.620000000000005</v>
+      </c>
+      <c r="J92">
+        <f t="shared" si="7"/>
+        <v>475</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>206</v>
       </c>
@@ -1666,6 +3123,22 @@
         <v>29</v>
       </c>
       <c r="E93">
+        <v>190</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="4"/>
+        <v>180.95</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="5"/>
+        <v>180.95</v>
+      </c>
+      <c r="I93">
+        <f t="shared" si="6"/>
+        <v>9.0500000000000114</v>
+      </c>
+      <c r="J93">
+        <f t="shared" si="7"/>
         <v>190</v>
       </c>
     </row>
@@ -1675,15 +3148,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{793928C9-9A63-4F00-8C61-5F5BBE767E80}">
-  <dimension ref="A2:E96"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A2:J96"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.6640625" customWidth="1"/>
     <col min="4" max="4" width="8.109375" customWidth="1"/>
+    <col min="6" max="6" width="28.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1699,8 +3173,11 @@
       <c r="E2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>34</v>
       </c>
@@ -1713,8 +3190,24 @@
       <c r="E4">
         <v>275</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <f>ROUND(IF(E4&gt;2500, E4/1.18, E4/1.05),2)</f>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H4">
+        <f>ROUND(IF(E4&gt;2500, E4/1.18, E4/1.05),2)</f>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="I4">
+        <f>E4-F4</f>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J4">
+        <f>SUM(H4:I4)</f>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>34</v>
       </c>
@@ -1727,8 +3220,24 @@
       <c r="E5">
         <v>375</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <f t="shared" ref="F5:F68" si="0">ROUND(IF(E5&gt;2500, E5/1.18, E5/1.05),2)</f>
+        <v>357.14</v>
+      </c>
+      <c r="H5">
+        <f t="shared" ref="H5:H68" si="1">ROUND(IF(E5&gt;2500, E5/1.18, E5/1.05),2)</f>
+        <v>357.14</v>
+      </c>
+      <c r="I5">
+        <f t="shared" ref="I5:I68" si="2">E5-F5</f>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J5">
+        <f t="shared" ref="J5:J68" si="3">SUM(H5:I5)</f>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>5624</v>
       </c>
@@ -1741,8 +3250,24 @@
       <c r="E6">
         <v>315</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="3"/>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>41</v>
       </c>
@@ -1755,8 +3280,24 @@
       <c r="E7">
         <v>435</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>414.29</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>414.29</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="2"/>
+        <v>20.70999999999998</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="3"/>
+        <v>435</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>41</v>
       </c>
@@ -1769,8 +3310,24 @@
       <c r="E8">
         <v>435</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>414.29</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>414.29</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="2"/>
+        <v>20.70999999999998</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="3"/>
+        <v>435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>1822</v>
       </c>
@@ -1783,8 +3340,24 @@
       <c r="E9">
         <v>175</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>166.67</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>166.67</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="2"/>
+        <v>8.3300000000000125</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>1821</v>
       </c>
@@ -1797,8 +3370,24 @@
       <c r="E10">
         <v>175</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>166.67</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>166.67</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="2"/>
+        <v>8.3300000000000125</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>5662</v>
       </c>
@@ -1811,8 +3400,24 @@
       <c r="E11">
         <v>160</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>152.38</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>152.38</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="2"/>
+        <v>7.6200000000000045</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="3"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>3357</v>
       </c>
@@ -1825,8 +3430,24 @@
       <c r="E12">
         <v>575</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>547.62</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>547.62</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="2"/>
+        <v>27.379999999999995</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="3"/>
+        <v>575</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>37</v>
       </c>
@@ -1839,8 +3460,24 @@
       <c r="E13">
         <v>440</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>419.05</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>419.05</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="2"/>
+        <v>20.949999999999989</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="3"/>
+        <v>440</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>5624</v>
       </c>
@@ -1853,8 +3490,24 @@
       <c r="E14">
         <v>315</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="3"/>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>43</v>
       </c>
@@ -1867,8 +3520,24 @@
       <c r="E15">
         <v>315</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="3"/>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>1301</v>
       </c>
@@ -1881,8 +3550,24 @@
       <c r="E16">
         <v>525</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="3"/>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>35</v>
       </c>
@@ -1895,8 +3580,24 @@
       <c r="E17">
         <v>290</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>276.19</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>276.19</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="2"/>
+        <v>13.810000000000002</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="3"/>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>1821</v>
       </c>
@@ -1909,8 +3610,24 @@
       <c r="E18">
         <v>175</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>166.67</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>166.67</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="2"/>
+        <v>8.3300000000000125</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>5627</v>
       </c>
@@ -1923,8 +3640,24 @@
       <c r="E19">
         <v>395</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>376.19</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>376.19</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="2"/>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="3"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>5627</v>
       </c>
@@ -1937,8 +3670,24 @@
       <c r="E20">
         <v>395</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>376.19</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>376.19</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="2"/>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="3"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>970</v>
       </c>
@@ -1951,8 +3700,24 @@
       <c r="E21">
         <v>285</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>271.43</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>271.43</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>13.569999999999993</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="3"/>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>5668</v>
       </c>
@@ -1965,8 +3730,24 @@
       <c r="E22">
         <v>215</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>204.76</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>204.76</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="2"/>
+        <v>10.240000000000009</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="3"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>5966</v>
       </c>
@@ -1979,8 +3760,24 @@
       <c r="E23">
         <v>455</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>433.33</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>433.33</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="2"/>
+        <v>21.670000000000016</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="3"/>
+        <v>455</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>35</v>
       </c>
@@ -1993,8 +3790,24 @@
       <c r="E24">
         <v>290</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>276.19</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>276.19</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="2"/>
+        <v>13.810000000000002</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="3"/>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>875</v>
       </c>
@@ -2007,8 +3820,24 @@
       <c r="E25">
         <v>285</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>271.43</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>271.43</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="2"/>
+        <v>13.569999999999993</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="3"/>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>3239</v>
       </c>
@@ -2021,8 +3850,24 @@
       <c r="E26">
         <v>265</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>252.38</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>252.38</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="2"/>
+        <v>12.620000000000005</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="3"/>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>5626</v>
       </c>
@@ -2035,8 +3880,24 @@
       <c r="E27">
         <v>185</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>176.19</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>176.19</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="2"/>
+        <v>8.8100000000000023</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>5626</v>
       </c>
@@ -2049,8 +3910,24 @@
       <c r="E28">
         <v>185</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>176.19</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="1"/>
+        <v>176.19</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="2"/>
+        <v>8.8100000000000023</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>5626</v>
       </c>
@@ -2063,8 +3940,24 @@
       <c r="E29">
         <v>185</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>176.19</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="1"/>
+        <v>176.19</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="2"/>
+        <v>8.8100000000000023</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>969</v>
       </c>
@@ -2077,8 +3970,24 @@
       <c r="E30">
         <v>175</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>166.67</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="1"/>
+        <v>166.67</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="2"/>
+        <v>8.3300000000000125</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>1821</v>
       </c>
@@ -2091,8 +4000,24 @@
       <c r="E31">
         <v>175</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>166.67</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="1"/>
+        <v>166.67</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="2"/>
+        <v>8.3300000000000125</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>1831</v>
       </c>
@@ -2105,8 +4030,24 @@
       <c r="E32">
         <v>175</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>166.67</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>166.67</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="2"/>
+        <v>8.3300000000000125</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>1299</v>
       </c>
@@ -2119,8 +4060,24 @@
       <c r="E33">
         <v>125</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>119.05</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="1"/>
+        <v>119.05</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="2"/>
+        <v>5.9500000000000028</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="3"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>5626</v>
       </c>
@@ -2133,8 +4090,24 @@
       <c r="E34">
         <v>185</v>
       </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>176.19</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>176.19</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="2"/>
+        <v>8.8100000000000023</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>1830</v>
       </c>
@@ -2147,8 +4120,24 @@
       <c r="E35">
         <v>175</v>
       </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>166.67</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="1"/>
+        <v>166.67</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="2"/>
+        <v>8.3300000000000125</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>1833</v>
       </c>
@@ -2161,8 +4150,24 @@
       <c r="E36">
         <v>345</v>
       </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>328.57</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="1"/>
+        <v>328.57</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="2"/>
+        <v>16.430000000000007</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="3"/>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>1300</v>
       </c>
@@ -2175,8 +4180,24 @@
       <c r="E37">
         <v>125</v>
       </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>119.05</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>119.05</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="2"/>
+        <v>5.9500000000000028</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="3"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>1842</v>
       </c>
@@ -2189,8 +4210,24 @@
       <c r="E38">
         <v>865</v>
       </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>823.81</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>823.81</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="2"/>
+        <v>41.190000000000055</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="3"/>
+        <v>865</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>5966</v>
       </c>
@@ -2203,8 +4240,24 @@
       <c r="E39">
         <v>455</v>
       </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>433.33</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="1"/>
+        <v>433.33</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="2"/>
+        <v>21.670000000000016</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="3"/>
+        <v>455</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>474</v>
       </c>
@@ -2217,8 +4270,24 @@
       <c r="E40">
         <v>295</v>
       </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>280.95</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>280.95</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="2"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="3"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>1839</v>
       </c>
@@ -2231,8 +4300,24 @@
       <c r="E41">
         <v>165</v>
       </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>157.13999999999999</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="1"/>
+        <v>157.13999999999999</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="2"/>
+        <v>7.8600000000000136</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="3"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>1821</v>
       </c>
@@ -2245,8 +4330,24 @@
       <c r="E42">
         <v>175</v>
       </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F42">
+        <f t="shared" si="0"/>
+        <v>166.67</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>166.67</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="2"/>
+        <v>8.3300000000000125</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>873</v>
       </c>
@@ -2259,8 +4360,24 @@
       <c r="E43">
         <v>325</v>
       </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F43">
+        <f t="shared" si="0"/>
+        <v>309.52</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="1"/>
+        <v>309.52</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="2"/>
+        <v>15.480000000000018</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="3"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>5219</v>
       </c>
@@ -2273,8 +4390,24 @@
       <c r="E44">
         <v>375</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F44">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="1"/>
+        <v>357.14</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>1761</v>
       </c>
@@ -2287,8 +4420,24 @@
       <c r="E45">
         <v>325</v>
       </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F45">
+        <f t="shared" si="0"/>
+        <v>309.52</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="1"/>
+        <v>309.52</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="2"/>
+        <v>15.480000000000018</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="3"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>873</v>
       </c>
@@ -2301,8 +4450,24 @@
       <c r="E46">
         <v>325</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F46">
+        <f t="shared" si="0"/>
+        <v>309.52</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="1"/>
+        <v>309.52</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="2"/>
+        <v>15.480000000000018</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="3"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>1821</v>
       </c>
@@ -2315,8 +4480,24 @@
       <c r="E47">
         <v>175</v>
       </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F47">
+        <f t="shared" si="0"/>
+        <v>166.67</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="1"/>
+        <v>166.67</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="2"/>
+        <v>8.3300000000000125</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>34</v>
       </c>
@@ -2329,8 +4510,24 @@
       <c r="E48">
         <v>275</v>
       </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F48">
+        <f t="shared" si="0"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="1"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="2"/>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="3"/>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>1829</v>
       </c>
@@ -2343,8 +4540,24 @@
       <c r="E49">
         <v>165</v>
       </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F49">
+        <f t="shared" si="0"/>
+        <v>157.13999999999999</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="1"/>
+        <v>157.13999999999999</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="2"/>
+        <v>7.8600000000000136</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="3"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>1821</v>
       </c>
@@ -2357,8 +4570,24 @@
       <c r="E50">
         <v>175</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F50">
+        <f t="shared" si="0"/>
+        <v>166.67</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="1"/>
+        <v>166.67</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="2"/>
+        <v>8.3300000000000125</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>3342</v>
       </c>
@@ -2371,8 +4600,24 @@
       <c r="E51">
         <v>210</v>
       </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F51">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="3"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>2808</v>
       </c>
@@ -2385,8 +4630,24 @@
       <c r="E52">
         <v>370</v>
       </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F52">
+        <f t="shared" si="0"/>
+        <v>352.38</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="1"/>
+        <v>352.38</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="2"/>
+        <v>17.620000000000005</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="3"/>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>2936</v>
       </c>
@@ -2399,8 +4660,24 @@
       <c r="E53">
         <v>825</v>
       </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F53">
+        <f t="shared" si="0"/>
+        <v>785.71</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="1"/>
+        <v>785.71</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="2"/>
+        <v>39.289999999999964</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="3"/>
+        <v>825</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>2931</v>
       </c>
@@ -2413,8 +4690,24 @@
       <c r="E54">
         <v>825</v>
       </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F54">
+        <f t="shared" si="0"/>
+        <v>785.71</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="1"/>
+        <v>785.71</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="2"/>
+        <v>39.289999999999964</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="3"/>
+        <v>825</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>3241</v>
       </c>
@@ -2427,8 +4720,24 @@
       <c r="E55">
         <v>735</v>
       </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F55">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="1"/>
+        <v>700</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="3"/>
+        <v>735</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>2775</v>
       </c>
@@ -2441,8 +4750,24 @@
       <c r="E56">
         <v>865</v>
       </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F56">
+        <f t="shared" si="0"/>
+        <v>823.81</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="1"/>
+        <v>823.81</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="2"/>
+        <v>41.190000000000055</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="3"/>
+        <v>865</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>2772</v>
       </c>
@@ -2455,8 +4780,24 @@
       <c r="E57">
         <v>565</v>
       </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F57">
+        <f t="shared" si="0"/>
+        <v>538.1</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="1"/>
+        <v>538.1</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="2"/>
+        <v>26.899999999999977</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="3"/>
+        <v>565</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>3144</v>
       </c>
@@ -2469,8 +4810,24 @@
       <c r="E58">
         <v>865</v>
       </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F58">
+        <f t="shared" si="0"/>
+        <v>823.81</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="1"/>
+        <v>823.81</v>
+      </c>
+      <c r="I58">
+        <f t="shared" si="2"/>
+        <v>41.190000000000055</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="3"/>
+        <v>865</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>3386</v>
       </c>
@@ -2483,8 +4840,24 @@
       <c r="E59">
         <v>585</v>
       </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F59">
+        <f t="shared" si="0"/>
+        <v>557.14</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="1"/>
+        <v>557.14</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="2"/>
+        <v>27.860000000000014</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="3"/>
+        <v>585</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>3255</v>
       </c>
@@ -2497,8 +4870,24 @@
       <c r="E60">
         <v>580</v>
       </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F60">
+        <f t="shared" si="0"/>
+        <v>552.38</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="1"/>
+        <v>552.38</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="2"/>
+        <v>27.620000000000005</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="3"/>
+        <v>580</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>3247</v>
       </c>
@@ -2511,8 +4900,24 @@
       <c r="E61">
         <v>795</v>
       </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F61">
+        <f t="shared" si="0"/>
+        <v>757.14</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="1"/>
+        <v>757.14</v>
+      </c>
+      <c r="I61">
+        <f t="shared" si="2"/>
+        <v>37.860000000000014</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="3"/>
+        <v>795</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>3234</v>
       </c>
@@ -2525,8 +4930,24 @@
       <c r="E62">
         <v>275</v>
       </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F62">
+        <f t="shared" si="0"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="1"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="I62">
+        <f t="shared" si="2"/>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="3"/>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>3236</v>
       </c>
@@ -2539,8 +4960,24 @@
       <c r="E63">
         <v>250</v>
       </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F63">
+        <f t="shared" si="0"/>
+        <v>238.1</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="1"/>
+        <v>238.1</v>
+      </c>
+      <c r="I63">
+        <f t="shared" si="2"/>
+        <v>11.900000000000006</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>3244</v>
       </c>
@@ -2553,8 +4990,24 @@
       <c r="E64">
         <v>645</v>
       </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F64">
+        <f t="shared" si="0"/>
+        <v>614.29</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="1"/>
+        <v>614.29</v>
+      </c>
+      <c r="I64">
+        <f t="shared" si="2"/>
+        <v>30.710000000000036</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="3"/>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>3238</v>
       </c>
@@ -2567,8 +5020,24 @@
       <c r="E65">
         <v>445</v>
       </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F65">
+        <f t="shared" si="0"/>
+        <v>423.81</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="1"/>
+        <v>423.81</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="2"/>
+        <v>21.189999999999998</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="3"/>
+        <v>445</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>3243</v>
       </c>
@@ -2581,8 +5050,24 @@
       <c r="E66">
         <v>675</v>
       </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F66">
+        <f t="shared" si="0"/>
+        <v>642.86</v>
+      </c>
+      <c r="H66">
+        <f t="shared" si="1"/>
+        <v>642.86</v>
+      </c>
+      <c r="I66">
+        <f t="shared" si="2"/>
+        <v>32.139999999999986</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="3"/>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>1793</v>
       </c>
@@ -2595,8 +5080,24 @@
       <c r="E67">
         <v>195</v>
       </c>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F67">
+        <f t="shared" si="0"/>
+        <v>185.71</v>
+      </c>
+      <c r="H67">
+        <f t="shared" si="1"/>
+        <v>185.71</v>
+      </c>
+      <c r="I67">
+        <f t="shared" si="2"/>
+        <v>9.289999999999992</v>
+      </c>
+      <c r="J67">
+        <f t="shared" si="3"/>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>1458</v>
       </c>
@@ -2609,8 +5110,24 @@
       <c r="E68">
         <v>220</v>
       </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F68">
+        <f t="shared" si="0"/>
+        <v>209.52</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="1"/>
+        <v>209.52</v>
+      </c>
+      <c r="I68">
+        <f t="shared" si="2"/>
+        <v>10.47999999999999</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="3"/>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>3238</v>
       </c>
@@ -2623,8 +5140,24 @@
       <c r="E69">
         <v>445</v>
       </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F69">
+        <f t="shared" ref="F69:F96" si="4">ROUND(IF(E69&gt;2500, E69/1.18, E69/1.05),2)</f>
+        <v>423.81</v>
+      </c>
+      <c r="H69">
+        <f t="shared" ref="H69:H96" si="5">ROUND(IF(E69&gt;2500, E69/1.18, E69/1.05),2)</f>
+        <v>423.81</v>
+      </c>
+      <c r="I69">
+        <f t="shared" ref="I69:I96" si="6">E69-F69</f>
+        <v>21.189999999999998</v>
+      </c>
+      <c r="J69">
+        <f t="shared" ref="J69:J96" si="7">SUM(H69:I69)</f>
+        <v>445</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>3234</v>
       </c>
@@ -2637,8 +5170,24 @@
       <c r="E70">
         <v>275</v>
       </c>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F70">
+        <f t="shared" si="4"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="5"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="I70">
+        <f t="shared" si="6"/>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="7"/>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>1837</v>
       </c>
@@ -2651,8 +5200,24 @@
       <c r="E71">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F71">
+        <f t="shared" si="4"/>
+        <v>66.67</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="5"/>
+        <v>66.67</v>
+      </c>
+      <c r="I71">
+        <f t="shared" si="6"/>
+        <v>3.3299999999999983</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="7"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>1793</v>
       </c>
@@ -2665,8 +5230,24 @@
       <c r="E72">
         <v>195</v>
       </c>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F72">
+        <f t="shared" si="4"/>
+        <v>185.71</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="5"/>
+        <v>185.71</v>
+      </c>
+      <c r="I72">
+        <f t="shared" si="6"/>
+        <v>9.289999999999992</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="7"/>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73" s="1">
         <v>3161</v>
       </c>
@@ -2679,8 +5260,24 @@
       <c r="E73" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F73">
+        <f t="shared" si="4"/>
+        <v>33.33</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="5"/>
+        <v>33.33</v>
+      </c>
+      <c r="I73">
+        <f t="shared" si="6"/>
+        <v>1.6700000000000017</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="7"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>2774</v>
       </c>
@@ -2693,8 +5290,24 @@
       <c r="E74">
         <v>775</v>
       </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F74">
+        <f t="shared" si="4"/>
+        <v>738.1</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="5"/>
+        <v>738.1</v>
+      </c>
+      <c r="I74">
+        <f t="shared" si="6"/>
+        <v>36.899999999999977</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="7"/>
+        <v>775</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>1132</v>
       </c>
@@ -2707,8 +5320,24 @@
       <c r="E75">
         <v>225</v>
       </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F75">
+        <f t="shared" si="4"/>
+        <v>214.29</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="5"/>
+        <v>214.29</v>
+      </c>
+      <c r="I75">
+        <f t="shared" si="6"/>
+        <v>10.710000000000008</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="7"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>2807</v>
       </c>
@@ -2721,8 +5350,24 @@
       <c r="E76">
         <v>290</v>
       </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F76">
+        <f t="shared" si="4"/>
+        <v>276.19</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="5"/>
+        <v>276.19</v>
+      </c>
+      <c r="I76">
+        <f t="shared" si="6"/>
+        <v>13.810000000000002</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="7"/>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>3235</v>
       </c>
@@ -2735,8 +5380,24 @@
       <c r="E77">
         <v>275</v>
       </c>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F77">
+        <f t="shared" si="4"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="5"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="I77">
+        <f t="shared" si="6"/>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="7"/>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>1836</v>
       </c>
@@ -2749,8 +5410,24 @@
       <c r="E78">
         <v>285</v>
       </c>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F78">
+        <f t="shared" si="4"/>
+        <v>271.43</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="5"/>
+        <v>271.43</v>
+      </c>
+      <c r="I78">
+        <f t="shared" si="6"/>
+        <v>13.569999999999993</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="7"/>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>2771</v>
       </c>
@@ -2763,8 +5440,24 @@
       <c r="E79">
         <v>475</v>
       </c>
-    </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F79">
+        <f t="shared" si="4"/>
+        <v>452.38</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="5"/>
+        <v>452.38</v>
+      </c>
+      <c r="I79">
+        <f t="shared" si="6"/>
+        <v>22.620000000000005</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="7"/>
+        <v>475</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>1131</v>
       </c>
@@ -2777,8 +5470,24 @@
       <c r="E80">
         <v>225</v>
       </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F80">
+        <f t="shared" si="4"/>
+        <v>214.29</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="5"/>
+        <v>214.29</v>
+      </c>
+      <c r="I80">
+        <f t="shared" si="6"/>
+        <v>10.710000000000008</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="7"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>1131</v>
       </c>
@@ -2791,8 +5500,24 @@
       <c r="E81">
         <v>225</v>
       </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F81">
+        <f t="shared" si="4"/>
+        <v>214.29</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="5"/>
+        <v>214.29</v>
+      </c>
+      <c r="I81">
+        <f t="shared" si="6"/>
+        <v>10.710000000000008</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="7"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>3240</v>
       </c>
@@ -2805,8 +5530,24 @@
       <c r="E82">
         <v>765</v>
       </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F82">
+        <f t="shared" si="4"/>
+        <v>728.57</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="5"/>
+        <v>728.57</v>
+      </c>
+      <c r="I82">
+        <f t="shared" si="6"/>
+        <v>36.42999999999995</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="7"/>
+        <v>765</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>3242</v>
       </c>
@@ -2819,8 +5560,24 @@
       <c r="E83">
         <v>845</v>
       </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F83">
+        <f t="shared" si="4"/>
+        <v>804.76</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="5"/>
+        <v>804.76</v>
+      </c>
+      <c r="I83">
+        <f t="shared" si="6"/>
+        <v>40.240000000000009</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="7"/>
+        <v>845</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>3242</v>
       </c>
@@ -2833,8 +5590,24 @@
       <c r="E84">
         <v>845</v>
       </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F84">
+        <f t="shared" si="4"/>
+        <v>804.76</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="5"/>
+        <v>804.76</v>
+      </c>
+      <c r="I84">
+        <f t="shared" si="6"/>
+        <v>40.240000000000009</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="7"/>
+        <v>845</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>174</v>
       </c>
@@ -2847,8 +5620,24 @@
       <c r="E85">
         <v>225</v>
       </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F85">
+        <f t="shared" si="4"/>
+        <v>214.29</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="5"/>
+        <v>214.29</v>
+      </c>
+      <c r="I85">
+        <f t="shared" si="6"/>
+        <v>10.710000000000008</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="7"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>2935</v>
       </c>
@@ -2861,8 +5650,24 @@
       <c r="E86">
         <v>1050</v>
       </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F86">
+        <f t="shared" si="4"/>
+        <v>1000</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="5"/>
+        <v>1000</v>
+      </c>
+      <c r="I86">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="7"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>3253</v>
       </c>
@@ -2875,8 +5680,24 @@
       <c r="E87">
         <v>675</v>
       </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F87">
+        <f t="shared" si="4"/>
+        <v>642.86</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="5"/>
+        <v>642.86</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="6"/>
+        <v>32.139999999999986</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="7"/>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>3340</v>
       </c>
@@ -2889,8 +5710,24 @@
       <c r="E88">
         <v>480</v>
       </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F88">
+        <f t="shared" si="4"/>
+        <v>457.14</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="5"/>
+        <v>457.14</v>
+      </c>
+      <c r="I88">
+        <f t="shared" si="6"/>
+        <v>22.860000000000014</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="7"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>8108</v>
       </c>
@@ -2903,8 +5740,24 @@
       <c r="E89">
         <v>155</v>
       </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F89">
+        <f t="shared" si="4"/>
+        <v>147.62</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="5"/>
+        <v>147.62</v>
+      </c>
+      <c r="I89">
+        <f t="shared" si="6"/>
+        <v>7.3799999999999955</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="7"/>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>1453</v>
       </c>
@@ -2917,8 +5770,24 @@
       <c r="E90">
         <v>165</v>
       </c>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F90">
+        <f t="shared" si="4"/>
+        <v>157.13999999999999</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="5"/>
+        <v>157.13999999999999</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="6"/>
+        <v>7.8600000000000136</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="7"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>4377</v>
       </c>
@@ -2931,8 +5800,24 @@
       <c r="E91">
         <v>275</v>
       </c>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F91">
+        <f t="shared" si="4"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="5"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="I91">
+        <f t="shared" si="6"/>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J91">
+        <f t="shared" si="7"/>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>1460</v>
       </c>
@@ -2945,8 +5830,24 @@
       <c r="E92">
         <v>285</v>
       </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F92">
+        <f t="shared" si="4"/>
+        <v>271.43</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="5"/>
+        <v>271.43</v>
+      </c>
+      <c r="I92">
+        <f t="shared" si="6"/>
+        <v>13.569999999999993</v>
+      </c>
+      <c r="J92">
+        <f t="shared" si="7"/>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>5242</v>
       </c>
@@ -2959,8 +5860,24 @@
       <c r="E93">
         <v>40</v>
       </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F93">
+        <f t="shared" si="4"/>
+        <v>38.1</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="5"/>
+        <v>38.1</v>
+      </c>
+      <c r="I93">
+        <f t="shared" si="6"/>
+        <v>1.8999999999999986</v>
+      </c>
+      <c r="J93">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>3128</v>
       </c>
@@ -2973,8 +5890,24 @@
       <c r="E94">
         <v>110</v>
       </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F94">
+        <f t="shared" si="4"/>
+        <v>104.76</v>
+      </c>
+      <c r="H94">
+        <f t="shared" si="5"/>
+        <v>104.76</v>
+      </c>
+      <c r="I94">
+        <f t="shared" si="6"/>
+        <v>5.2399999999999949</v>
+      </c>
+      <c r="J94">
+        <f t="shared" si="7"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95">
         <v>1461</v>
       </c>
@@ -2987,8 +5920,24 @@
       <c r="E95">
         <v>285</v>
       </c>
-    </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F95">
+        <f t="shared" si="4"/>
+        <v>271.43</v>
+      </c>
+      <c r="H95">
+        <f t="shared" si="5"/>
+        <v>271.43</v>
+      </c>
+      <c r="I95">
+        <f t="shared" si="6"/>
+        <v>13.569999999999993</v>
+      </c>
+      <c r="J95">
+        <f t="shared" si="7"/>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B96">
         <v>5242</v>
       </c>
@@ -2999,6 +5948,22 @@
         <v>84</v>
       </c>
       <c r="E96">
+        <v>40</v>
+      </c>
+      <c r="F96">
+        <f t="shared" si="4"/>
+        <v>38.1</v>
+      </c>
+      <c r="H96">
+        <f t="shared" si="5"/>
+        <v>38.1</v>
+      </c>
+      <c r="I96">
+        <f t="shared" si="6"/>
+        <v>1.8999999999999986</v>
+      </c>
+      <c r="J96">
+        <f t="shared" si="7"/>
         <v>40</v>
       </c>
     </row>
@@ -3008,17 +5973,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24107CE0-6E4E-4945-83B7-27746F8B6C78}">
-  <dimension ref="A2:E53"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A2:J53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.33203125" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" customWidth="1"/>
     <col min="4" max="4" width="12.44140625" customWidth="1"/>
     <col min="5" max="5" width="10.109375" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3034,8 +6001,20 @@
       <c r="E2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>872</v>
       </c>
@@ -3048,8 +6027,24 @@
       <c r="E3">
         <v>115</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <f>ROUND(IF(E3&gt;2500, E3/1.18, E3/1.05),2)</f>
+        <v>109.52</v>
+      </c>
+      <c r="H3">
+        <f>E3/1.05</f>
+        <v>109.52380952380952</v>
+      </c>
+      <c r="I3">
+        <f>E3-F3</f>
+        <v>5.480000000000004</v>
+      </c>
+      <c r="J3" s="2">
+        <f>SUM(H3:I3)</f>
+        <v>115.00380952380952</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>872</v>
       </c>
@@ -3062,8 +6057,24 @@
       <c r="E4">
         <v>115</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <f t="shared" ref="F4:F53" si="0">ROUND(IF(E4&gt;2500, E4/1.18, E4/1.05),2)</f>
+        <v>109.52</v>
+      </c>
+      <c r="H4">
+        <f t="shared" ref="H4:H53" si="1">E4/1.05</f>
+        <v>109.52380952380952</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I4:I53" si="2">E4-F4</f>
+        <v>5.480000000000004</v>
+      </c>
+      <c r="J4" s="2">
+        <f t="shared" ref="J4:J52" si="3">SUM(H4:I4)</f>
+        <v>115.00380952380952</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>872</v>
       </c>
@@ -3076,8 +6087,24 @@
       <c r="E5">
         <v>115</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>109.52</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>109.52380952380952</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="2"/>
+        <v>5.480000000000004</v>
+      </c>
+      <c r="J5" s="2">
+        <f t="shared" si="3"/>
+        <v>115.00380952380952</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>2782</v>
       </c>
@@ -3090,8 +6117,24 @@
       <c r="E6">
         <v>315</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="J6" s="2">
+        <f t="shared" si="3"/>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>872</v>
       </c>
@@ -3104,8 +6147,24 @@
       <c r="E7">
         <v>115</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>109.52</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>109.52380952380952</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="2"/>
+        <v>5.480000000000004</v>
+      </c>
+      <c r="J7" s="2">
+        <f t="shared" si="3"/>
+        <v>115.00380952380952</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>3334</v>
       </c>
@@ -3118,8 +6177,24 @@
       <c r="E8">
         <v>275</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>261.90476190476187</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="2"/>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J8" s="2">
+        <f t="shared" si="3"/>
+        <v>275.00476190476189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>2805</v>
       </c>
@@ -3132,8 +6207,24 @@
       <c r="E9">
         <v>135</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>128.57</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>128.57142857142856</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="2"/>
+        <v>6.4300000000000068</v>
+      </c>
+      <c r="J9" s="2">
+        <f t="shared" si="3"/>
+        <v>135.00142857142856</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>3251</v>
       </c>
@@ -3146,8 +6237,24 @@
       <c r="E10">
         <v>305</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>290.48</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>290.47619047619048</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="2"/>
+        <v>14.519999999999982</v>
+      </c>
+      <c r="J10" s="2">
+        <f t="shared" si="3"/>
+        <v>304.99619047619046</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>2805</v>
       </c>
@@ -3160,8 +6267,24 @@
       <c r="E11">
         <v>135</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>128.57</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>128.57142857142856</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="2"/>
+        <v>6.4300000000000068</v>
+      </c>
+      <c r="J11" s="2">
+        <f t="shared" si="3"/>
+        <v>135.00142857142856</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>3111</v>
       </c>
@@ -3174,8 +6297,24 @@
       <c r="E12">
         <v>220</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>209.52</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>209.52380952380952</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="2"/>
+        <v>10.47999999999999</v>
+      </c>
+      <c r="J12" s="2">
+        <f t="shared" si="3"/>
+        <v>220.00380952380951</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>2809</v>
       </c>
@@ -3188,8 +6327,24 @@
       <c r="E13">
         <v>240</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>228.57</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>228.57142857142856</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="2"/>
+        <v>11.430000000000007</v>
+      </c>
+      <c r="J13" s="2">
+        <f t="shared" si="3"/>
+        <v>240.00142857142856</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>3111</v>
       </c>
@@ -3202,8 +6357,24 @@
       <c r="E14">
         <v>220</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>209.52</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>209.52380952380952</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="2"/>
+        <v>10.47999999999999</v>
+      </c>
+      <c r="J14" s="2">
+        <f t="shared" si="3"/>
+        <v>220.00380952380951</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>1841</v>
       </c>
@@ -3216,8 +6387,24 @@
       <c r="E15">
         <v>55</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>52.38</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>52.38095238095238</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="2"/>
+        <v>2.6199999999999974</v>
+      </c>
+      <c r="J15" s="2">
+        <f t="shared" si="3"/>
+        <v>55.000952380952377</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>3249</v>
       </c>
@@ -3230,8 +6417,24 @@
       <c r="E16">
         <v>495</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>471.43</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>471.42857142857139</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="2"/>
+        <v>23.569999999999993</v>
+      </c>
+      <c r="J16" s="2">
+        <f t="shared" si="3"/>
+        <v>494.99857142857138</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>1335</v>
       </c>
@@ -3244,8 +6447,24 @@
       <c r="E17">
         <v>155</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>147.62</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>147.61904761904762</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="2"/>
+        <v>7.3799999999999955</v>
+      </c>
+      <c r="J17" s="2">
+        <f t="shared" si="3"/>
+        <v>154.99904761904762</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>3114</v>
       </c>
@@ -3258,8 +6477,24 @@
       <c r="E18">
         <v>170</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>161.9</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>161.9047619047619</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="2"/>
+        <v>8.0999999999999943</v>
+      </c>
+      <c r="J18" s="2">
+        <f t="shared" si="3"/>
+        <v>170.00476190476189</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>5039</v>
       </c>
@@ -3272,8 +6507,24 @@
       <c r="E19">
         <v>210</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J19" s="2">
+        <f t="shared" si="3"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>1128</v>
       </c>
@@ -3286,8 +6537,24 @@
       <c r="E20">
         <v>225</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>214.29</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>214.28571428571428</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="2"/>
+        <v>10.710000000000008</v>
+      </c>
+      <c r="J20" s="2">
+        <f t="shared" si="3"/>
+        <v>224.99571428571429</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>3126</v>
       </c>
@@ -3300,8 +6567,24 @@
       <c r="E21">
         <v>95</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>90.48</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>90.476190476190467</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>4.519999999999996</v>
+      </c>
+      <c r="J21" s="2">
+        <f t="shared" si="3"/>
+        <v>94.996190476190463</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>5040</v>
       </c>
@@ -3314,8 +6597,24 @@
       <c r="E22">
         <v>190</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>180.95</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>180.95238095238093</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="2"/>
+        <v>9.0500000000000114</v>
+      </c>
+      <c r="J22" s="2">
+        <f t="shared" si="3"/>
+        <v>190.00238095238095</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>42</v>
       </c>
@@ -3328,8 +6627,24 @@
       <c r="E23">
         <v>835</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>795.24</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>795.23809523809518</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="2"/>
+        <v>39.759999999999991</v>
+      </c>
+      <c r="J23" s="2">
+        <f t="shared" si="3"/>
+        <v>834.99809523809517</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>1454</v>
       </c>
@@ -3342,8 +6657,24 @@
       <c r="E24">
         <v>170</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>161.9</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>161.9047619047619</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="2"/>
+        <v>8.0999999999999943</v>
+      </c>
+      <c r="J24" s="2">
+        <f t="shared" si="3"/>
+        <v>170.00476190476189</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>3230</v>
       </c>
@@ -3356,8 +6687,24 @@
       <c r="E25">
         <v>350</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>333.33</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="2"/>
+        <v>16.670000000000016</v>
+      </c>
+      <c r="J25" s="2">
+        <f t="shared" si="3"/>
+        <v>350.00333333333333</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>3120</v>
       </c>
@@ -3370,8 +6717,24 @@
       <c r="E26">
         <v>225</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>214.29</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>214.28571428571428</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="2"/>
+        <v>10.710000000000008</v>
+      </c>
+      <c r="J26" s="2">
+        <f t="shared" si="3"/>
+        <v>224.99571428571429</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>3113</v>
       </c>
@@ -3384,8 +6747,24 @@
       <c r="E27">
         <v>135</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>128.57</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>128.57142857142856</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="2"/>
+        <v>6.4300000000000068</v>
+      </c>
+      <c r="J27" s="2">
+        <f t="shared" si="3"/>
+        <v>135.00142857142856</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>1457</v>
       </c>
@@ -3398,8 +6777,24 @@
       <c r="E28">
         <v>155</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>147.62</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="1"/>
+        <v>147.61904761904762</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="2"/>
+        <v>7.3799999999999955</v>
+      </c>
+      <c r="J28" s="2">
+        <f t="shared" si="3"/>
+        <v>154.99904761904762</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>5037</v>
       </c>
@@ -3412,8 +6807,24 @@
       <c r="E29">
         <v>135</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>128.57</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="1"/>
+        <v>128.57142857142856</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="2"/>
+        <v>6.4300000000000068</v>
+      </c>
+      <c r="J29" s="2">
+        <f t="shared" si="3"/>
+        <v>135.00142857142856</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>3124</v>
       </c>
@@ -3426,8 +6837,24 @@
       <c r="E30">
         <v>220</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>209.52</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="1"/>
+        <v>209.52380952380952</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="2"/>
+        <v>10.47999999999999</v>
+      </c>
+      <c r="J30" s="2">
+        <f t="shared" si="3"/>
+        <v>220.00380952380951</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>3117</v>
       </c>
@@ -3440,8 +6867,24 @@
       <c r="E31">
         <v>230</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>219.05</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="1"/>
+        <v>219.04761904761904</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="2"/>
+        <v>10.949999999999989</v>
+      </c>
+      <c r="J31" s="2">
+        <f t="shared" si="3"/>
+        <v>229.99761904761903</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>3109</v>
       </c>
@@ -3454,8 +6897,24 @@
       <c r="E32">
         <v>150</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>142.86000000000001</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>142.85714285714286</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="2"/>
+        <v>7.1399999999999864</v>
+      </c>
+      <c r="J32" s="2">
+        <f t="shared" si="3"/>
+        <v>149.99714285714285</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>1835</v>
       </c>
@@ -3468,8 +6927,24 @@
       <c r="E33">
         <v>155</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>147.62</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="1"/>
+        <v>147.61904761904762</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="2"/>
+        <v>7.3799999999999955</v>
+      </c>
+      <c r="J33" s="2">
+        <f t="shared" si="3"/>
+        <v>154.99904761904762</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>1294</v>
       </c>
@@ -3482,8 +6957,24 @@
       <c r="E34">
         <v>95</v>
       </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>90.48</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>90.476190476190467</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="2"/>
+        <v>4.519999999999996</v>
+      </c>
+      <c r="J34" s="2">
+        <f t="shared" si="3"/>
+        <v>94.996190476190463</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>3117</v>
       </c>
@@ -3496,8 +6987,24 @@
       <c r="E35">
         <v>230</v>
       </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>219.05</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="1"/>
+        <v>219.04761904761904</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="2"/>
+        <v>10.949999999999989</v>
+      </c>
+      <c r="J35" s="2">
+        <f t="shared" si="3"/>
+        <v>229.99761904761903</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>3161</v>
       </c>
@@ -3510,8 +7017,24 @@
       <c r="E36">
         <v>200</v>
       </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>190.48</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="1"/>
+        <v>190.47619047619048</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="2"/>
+        <v>9.5200000000000102</v>
+      </c>
+      <c r="J36" s="2">
+        <f t="shared" si="3"/>
+        <v>199.99619047619049</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>1455</v>
       </c>
@@ -3524,8 +7047,24 @@
       <c r="E37">
         <v>140</v>
       </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>133.33000000000001</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>133.33333333333331</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="2"/>
+        <v>6.6699999999999875</v>
+      </c>
+      <c r="J37" s="2">
+        <f t="shared" si="3"/>
+        <v>140.0033333333333</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>1459</v>
       </c>
@@ -3538,8 +7077,24 @@
       <c r="E38">
         <v>165</v>
       </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>157.13999999999999</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>157.14285714285714</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="2"/>
+        <v>7.8600000000000136</v>
+      </c>
+      <c r="J38" s="2">
+        <f t="shared" si="3"/>
+        <v>165.00285714285715</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>1294</v>
       </c>
@@ -3552,8 +7107,24 @@
       <c r="E39">
         <v>95</v>
       </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>90.48</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="1"/>
+        <v>90.476190476190467</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="2"/>
+        <v>4.519999999999996</v>
+      </c>
+      <c r="J39" s="2">
+        <f t="shared" si="3"/>
+        <v>94.996190476190463</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>3110</v>
       </c>
@@ -3566,8 +7137,24 @@
       <c r="E40">
         <v>155</v>
       </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>147.62</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>147.61904761904762</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="2"/>
+        <v>7.3799999999999955</v>
+      </c>
+      <c r="J40" s="2">
+        <f t="shared" si="3"/>
+        <v>154.99904761904762</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>2808</v>
       </c>
@@ -3580,8 +7167,24 @@
       <c r="E41">
         <v>370</v>
       </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>352.38</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="1"/>
+        <v>352.38095238095235</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="2"/>
+        <v>17.620000000000005</v>
+      </c>
+      <c r="J41" s="2">
+        <f t="shared" si="3"/>
+        <v>370.00095238095236</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>2809</v>
       </c>
@@ -3594,8 +7197,24 @@
       <c r="E42">
         <v>240</v>
       </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F42">
+        <f t="shared" si="0"/>
+        <v>228.57</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>228.57142857142856</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="2"/>
+        <v>11.430000000000007</v>
+      </c>
+      <c r="J42" s="2">
+        <f t="shared" si="3"/>
+        <v>240.00142857142856</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>474</v>
       </c>
@@ -3608,8 +7227,24 @@
       <c r="E43">
         <v>295</v>
       </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F43">
+        <f t="shared" si="0"/>
+        <v>280.95</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="1"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="2"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J43" s="2">
+        <f t="shared" si="3"/>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>1593</v>
       </c>
@@ -3622,8 +7257,24 @@
       <c r="E44">
         <v>475</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F44">
+        <f t="shared" si="0"/>
+        <v>452.38</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="1"/>
+        <v>452.38095238095235</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="2"/>
+        <v>22.620000000000005</v>
+      </c>
+      <c r="J44" s="2">
+        <f t="shared" si="3"/>
+        <v>475.00095238095236</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>1592</v>
       </c>
@@ -3636,8 +7287,24 @@
       <c r="E45">
         <v>450</v>
       </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F45">
+        <f t="shared" si="0"/>
+        <v>428.57</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="1"/>
+        <v>428.57142857142856</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="2"/>
+        <v>21.430000000000007</v>
+      </c>
+      <c r="J45" s="2">
+        <f t="shared" si="3"/>
+        <v>450.00142857142856</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>1835</v>
       </c>
@@ -3650,8 +7317,24 @@
       <c r="E46">
         <v>155</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F46">
+        <f t="shared" si="0"/>
+        <v>147.62</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="1"/>
+        <v>147.61904761904762</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="2"/>
+        <v>7.3799999999999955</v>
+      </c>
+      <c r="J46" s="2">
+        <f t="shared" si="3"/>
+        <v>154.99904761904762</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>1330</v>
       </c>
@@ -3664,8 +7347,24 @@
       <c r="E47">
         <v>195</v>
       </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F47">
+        <f t="shared" si="0"/>
+        <v>185.71</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="1"/>
+        <v>185.71428571428569</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="2"/>
+        <v>9.289999999999992</v>
+      </c>
+      <c r="J47" s="2">
+        <f t="shared" si="3"/>
+        <v>195.00428571428569</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>3235</v>
       </c>
@@ -3678,8 +7377,24 @@
       <c r="E48">
         <v>295</v>
       </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F48">
+        <f t="shared" si="0"/>
+        <v>280.95</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="1"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="2"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J48" s="2">
+        <f t="shared" si="3"/>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>3119</v>
       </c>
@@ -3692,8 +7407,24 @@
       <c r="E49">
         <v>545</v>
       </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F49">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="2"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J49" s="2">
+        <f t="shared" si="3"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>1452</v>
       </c>
@@ -3706,8 +7437,24 @@
       <c r="E50">
         <v>195</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F50">
+        <f t="shared" si="0"/>
+        <v>185.71</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="1"/>
+        <v>185.71428571428569</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="2"/>
+        <v>9.289999999999992</v>
+      </c>
+      <c r="J50" s="2">
+        <f t="shared" si="3"/>
+        <v>195.00428571428569</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>3234</v>
       </c>
@@ -3720,8 +7467,24 @@
       <c r="E51">
         <v>275</v>
       </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F51">
+        <f t="shared" si="0"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="1"/>
+        <v>261.90476190476187</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="2"/>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J51" s="2">
+        <f t="shared" si="3"/>
+        <v>275.00476190476189</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>3339</v>
       </c>
@@ -3734,8 +7497,24 @@
       <c r="E52">
         <v>495</v>
       </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F52">
+        <f t="shared" si="0"/>
+        <v>471.43</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="1"/>
+        <v>471.42857142857139</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="2"/>
+        <v>23.569999999999993</v>
+      </c>
+      <c r="J52" s="2">
+        <f t="shared" si="3"/>
+        <v>494.99857142857138</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>5220</v>
       </c>
@@ -3747,6 +7526,22 @@
       </c>
       <c r="E53">
         <v>475</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="0"/>
+        <v>452.38</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="1"/>
+        <v>452.38095238095235</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="2"/>
+        <v>22.620000000000005</v>
+      </c>
+      <c r="J53" s="2">
+        <f>SUM(H53:I53)</f>
+        <v>475.00095238095236</v>
       </c>
     </row>
   </sheetData>
